--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 10/front/old/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 10/front/old/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.61427</v>
+        <v>16.67494</v>
       </c>
       <c r="D2" t="n">
-        <v>16.36313</v>
+        <v>16.35497</v>
       </c>
       <c r="E2" t="n">
-        <v>16.51549</v>
+        <v>16.59071</v>
       </c>
       <c r="F2" t="n">
-        <v>42.51945</v>
+        <v>41.79194</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04968</v>
+        <v>0.05005</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80213</v>
+        <v>1.82955</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83002</v>
+        <v>16.50609</v>
       </c>
       <c r="D3" t="n">
-        <v>16.18844</v>
+        <v>16.31424</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5672</v>
+        <v>16.50323</v>
       </c>
       <c r="F3" t="n">
-        <v>41.0546</v>
+        <v>41.79316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05002</v>
+        <v>0.04994</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80402</v>
+        <v>1.77121</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.4257</v>
+        <v>16.59171</v>
       </c>
       <c r="D4" t="n">
-        <v>16.20205</v>
+        <v>16.04669</v>
       </c>
       <c r="E4" t="n">
-        <v>16.5765</v>
+        <v>16.23605</v>
       </c>
       <c r="F4" t="n">
-        <v>41.49408</v>
+        <v>43.35993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04947</v>
+        <v>0.05194</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84762</v>
+        <v>1.81168</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.91006</v>
+        <v>16.61329</v>
       </c>
       <c r="D5" t="n">
-        <v>16.39147</v>
+        <v>16.27358</v>
       </c>
       <c r="E5" t="n">
-        <v>16.47064</v>
+        <v>16.4934</v>
       </c>
       <c r="F5" t="n">
-        <v>41.457</v>
+        <v>42.48164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04959</v>
+        <v>0.05017</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80991</v>
+        <v>1.78363</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.49763</v>
+        <v>17.2152</v>
       </c>
       <c r="D6" t="n">
-        <v>16.39291</v>
+        <v>16.31975</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5866</v>
+        <v>16.46483</v>
       </c>
       <c r="F6" t="n">
-        <v>41.37073</v>
+        <v>42.22428</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05097</v>
+        <v>0.04987</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81628</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.47403</v>
+        <v>16.72899</v>
       </c>
       <c r="D7" t="n">
-        <v>16.48553</v>
+        <v>16.10254</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67259</v>
+        <v>16.46759</v>
       </c>
       <c r="F7" t="n">
-        <v>41.84192</v>
+        <v>41.71948</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05028</v>
+        <v>0.04903</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81224</v>
+        <v>1.7958</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.65825</v>
+        <v>16.657</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20252</v>
+        <v>16.59674</v>
       </c>
       <c r="E8" t="n">
-        <v>16.64636</v>
+        <v>16.64037</v>
       </c>
       <c r="F8" t="n">
-        <v>42.89771</v>
+        <v>42.28188</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05043</v>
+        <v>0.05014</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79841</v>
+        <v>1.79002</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.8312</v>
+        <v>16.89043</v>
       </c>
       <c r="D9" t="n">
-        <v>16.1304</v>
+        <v>16.40152</v>
       </c>
       <c r="E9" t="n">
-        <v>16.29524</v>
+        <v>16.70106</v>
       </c>
       <c r="F9" t="n">
-        <v>42.49652</v>
+        <v>41.38672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05127</v>
+        <v>0.04938</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79087</v>
+        <v>1.80479</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.53547</v>
+        <v>16.47468</v>
       </c>
       <c r="D10" t="n">
-        <v>16.60042</v>
+        <v>16.19762</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45727</v>
+        <v>16.37912</v>
       </c>
       <c r="F10" t="n">
-        <v>41.92977</v>
+        <v>42.3119</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04931</v>
+        <v>0.04962</v>
       </c>
       <c r="H10" t="n">
-        <v>1.80996</v>
+        <v>1.79573</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60733</v>
+        <v>0.6021300000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10599</v>
+        <v>1.09296</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60754</v>
+        <v>0.6021</v>
       </c>
       <c r="D13" t="n">
-        <v>1.08686</v>
+        <v>1.1207</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60294</v>
+        <v>0.60671</v>
       </c>
       <c r="D14" t="n">
-        <v>1.12496</v>
+        <v>1.10227</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59904</v>
+        <v>0.59732</v>
       </c>
       <c r="D15" t="n">
-        <v>1.09123</v>
+        <v>1.11775</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.59955</v>
+        <v>0.60237</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08169</v>
+        <v>1.10808</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59945</v>
+        <v>0.5992</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10299</v>
+        <v>1.11029</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59685</v>
+        <v>0.61106</v>
       </c>
       <c r="D18" t="n">
-        <v>1.07183</v>
+        <v>1.11762</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.59179</v>
+        <v>0.60759</v>
       </c>
       <c r="D19" t="n">
-        <v>1.09142</v>
+        <v>1.10017</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60694</v>
+        <v>0.6072</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10321</v>
+        <v>1.10781</v>
       </c>
     </row>
   </sheetData>
